--- a/etf_holdings/2026-09-29_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-09-29_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV17"/>
+  <dimension ref="A1:BV20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,102 +539,102 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>00982A_異動類型</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>00982A_調整方向</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>00982A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>00982A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>00982A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>00982A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>00982A_權重變化</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>00982A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>00982A_股數_今日</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>00982A_股數變化</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
           <t>00403A_異動類型</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>00403A_調整方向</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>00403A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>00403A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>00403A_權重_昨日</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>00403A_權重_今日</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>00403A_權重變化</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>00403A_股數_昨日</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>00403A_股數_今日</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>00403A_股數變化</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>00985A_異動類型</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>00985A_調整方向</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>00985A_股票名稱_昨日</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>00985A_股票名稱_今日</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>00985A_權重_昨日</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>00985A_權重_今日</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>00985A_權重變化</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>00985A_股數_昨日</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>00985A_股數_今日</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>00985A_股數變化</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
@@ -791,12 +791,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -804,7 +804,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00985A,00991A,00993A</t>
+          <t>00403A,00982A,00991A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -824,55 +824,91 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>5.55%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>+5.24%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>4400000</v>
+        <v>740000</v>
       </c>
       <c r="W2" t="n">
-        <v>4500000</v>
+        <v>430000</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>100,000</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
+          <t>-310,000</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2.31%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2.02%</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>621000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>541000</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-80,000</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>持續持有</t>
@@ -885,38 +921,38 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>196000</v>
+        <v>1900000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>118000</v>
+        <v>1800000</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-78,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
@@ -929,52 +965,16 @@
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>景碩科技</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>3.77%</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>4.01%</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>+0.24%</t>
-        </is>
-      </c>
-      <c r="BJ2" t="n">
-        <v>428000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>431000</v>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="inlineStr"/>
       <c r="BO2" t="inlineStr"/>
@@ -989,12 +989,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00400A,00403A,00993A</t>
+          <t>00403A,00982A,00993A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -1037,50 +1037,86 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>3.69%</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>646000</v>
+        <v>820000</v>
       </c>
       <c r="AG3" t="n">
-        <v>610000</v>
+        <v>815000</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-36,000</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
+          <t>-5,000</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>310000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>140000</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-170,000</t>
+        </is>
+      </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
@@ -1103,96 +1139,60 @@
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>創意電子</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>5.29%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>5.45%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>65000</v>
+        <v>14000</v>
       </c>
       <c r="BK3" t="n">
-        <v>66000</v>
+        <v>15000</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
           <t>1,000</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>5.04%</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>4.27%</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>-0.77%</t>
-        </is>
-      </c>
-      <c r="BT3" t="n">
-        <v>173000</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>155000</v>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>-18,000</t>
-        </is>
-      </c>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00985A,00991A,00993A</t>
+          <t>00400A,00403A,00993A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -1213,52 +1213,16 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>南亞電路</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>+0.13%</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>5.57%</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>+5.44%</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>100,000</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
@@ -1281,38 +1245,38 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>南亞電路板</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>192000</v>
+        <v>646000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>128000</v>
+        <v>610000</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-64,000</t>
+          <t>-36,000</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
@@ -1337,136 +1301,208 @@
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>創意電子</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>5.29%</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>5.45%</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>247000</v>
+        <v>65000</v>
       </c>
       <c r="BK4" t="n">
-        <v>254000</v>
+        <v>66000</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>7,000</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>5.04%</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>4.27%</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>-0.77%</t>
+        </is>
+      </c>
+      <c r="BT4" t="n">
+        <v>173000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>155000</v>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>-18,000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00991A,00992A</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>南亞塑膠</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>+0.09%</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>+2.14%</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>6700000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>300,000</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
+          <t>00981A,00982A,00993A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3.36%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3.14%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>13966000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>12966000</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-1,000,000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>906000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>876000</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>-30,000</t>
+        </is>
+      </c>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
@@ -1477,62 +1513,62 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>2.94%</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>2.06%</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>-0.88%</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>5445000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3645000</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-1,800,000</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>76000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>85000</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="inlineStr"/>
@@ -1547,12 +1583,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1560,7 +1596,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00991A,00993A</t>
+          <t>00991A,00992A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -1580,43 +1616,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>國巨股份</t>
+          <t>南亞塑膠</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>+4.19%</t>
+          <t>+2.14%</t>
         </is>
       </c>
       <c r="V6" t="n">
         <v>6700000</v>
       </c>
       <c r="W6" t="n">
-        <v>6000000</v>
+        <v>7000000</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-700,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1639,62 +1675,62 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2.03%</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2.18%</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>+0.15%</t>
-        </is>
-      </c>
-      <c r="BJ6" t="n">
-        <v>365000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>388000</v>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>23,000</t>
-        </is>
-      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>2.94%</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>2.06%</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>-0.88%</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>5445000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>3645000</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-1,800,000</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="inlineStr"/>
@@ -1709,12 +1745,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1722,7 +1758,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00991A,00993A</t>
+          <t>00982A,00993A</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -1735,62 +1771,62 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>台灣積體</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>-0.12%</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>12.78%</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>+12.90%</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="W7" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>200,000</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>1.82%</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>3230000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3216000</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>-14,000</t>
+        </is>
+      </c>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
@@ -1823,38 +1859,38 @@
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>8.42%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>8.32%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>347000</v>
+        <v>80000</v>
       </c>
       <c r="BK7" t="n">
-        <v>349000</v>
+        <v>89000</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr"/>
@@ -1871,12 +1907,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1884,7 +1920,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00403A,00991A</t>
+          <t>00982A,00993A</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1897,96 +1933,60 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>智邦科技</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>1.00%</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>+1.00%</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>740000</v>
-      </c>
-      <c r="W8" t="n">
-        <v>430000</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>-310,000</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="AF8" t="n">
-        <v>1900000</v>
+        <v>5145000</v>
       </c>
       <c r="AG8" t="n">
-        <v>1800000</v>
+        <v>5116000</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-100,000</t>
+          <t>-29,000</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr"/>
@@ -2009,16 +2009,52 @@
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2.89%</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1835000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1938000</v>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>103,000</t>
+        </is>
+      </c>
       <c r="BM8" t="inlineStr"/>
       <c r="BN8" t="inlineStr"/>
       <c r="BO8" t="inlineStr"/>
@@ -2033,12 +2069,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2046,7 +2082,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00403A,00993A</t>
+          <t>00991A,00993A</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -2059,62 +2095,62 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>0.48%</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>0.21%</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>-0.27%</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>310000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>140000</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-170,000</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>國巨股份</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>+0.06%</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4.25%</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>+4.19%</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>6700000</v>
+      </c>
+      <c r="W9" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-700,000</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
@@ -2147,38 +2183,38 @@
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>2.18%</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>14000</v>
+        <v>365000</v>
       </c>
       <c r="BK9" t="n">
-        <v>15000</v>
+        <v>388000</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr"/>
@@ -2195,12 +2231,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2208,7 +2244,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00400A,00991A</t>
+          <t>00991A,00993A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -2233,38 +2269,38 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>聯發科技</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7.16%</t>
+          <t>12.78%</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>+7.02%</t>
+          <t>+12.90%</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>1080000</v>
+        <v>3800000</v>
       </c>
       <c r="W10" t="n">
-        <v>1130000</v>
+        <v>4000000</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -2297,72 +2333,72 @@
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>7.99%</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>7.06%</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>-0.93%</t>
-        </is>
-      </c>
-      <c r="BT10" t="n">
-        <v>442000</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>413000</v>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>-29,000</t>
-        </is>
-      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>8.42%</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>8.32%</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>347000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>349000</v>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2370,7 +2406,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00403A,00993A</t>
+          <t>00982A,00993A</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -2405,38 +2441,38 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>6.81%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5.84%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>2850000</v>
+        <v>311000</v>
       </c>
       <c r="AG11" t="n">
-        <v>2500000</v>
+        <v>309000</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-350,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr"/>
@@ -2471,38 +2507,38 @@
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>5.33%</t>
+          <t>4.88%</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>5.65%</t>
+          <t>4.94%</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>158000</v>
+        <v>100000</v>
       </c>
       <c r="BK11" t="n">
-        <v>164000</v>
+        <v>101000</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr"/>
@@ -2519,12 +2555,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2532,7 +2568,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00991A,00993A</t>
+          <t>00982A,00993A</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -2545,62 +2581,62 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>欣興電子</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>+0.16%</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>7.82%</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>+7.66%</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="W12" t="n">
-        <v>5200000</v>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>100,000</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1.56%</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
+        <v>1128000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>964000</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>-164,000</t>
+        </is>
+      </c>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
@@ -2633,38 +2669,38 @@
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>5.54%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>5.96%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>492000</v>
+        <v>76000</v>
       </c>
       <c r="BK12" t="n">
-        <v>519000</v>
+        <v>84000</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr"/>
@@ -2681,12 +2717,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2694,7 +2730,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00400A,00991A</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -2707,16 +2743,52 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>聯發科技</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>7.16%</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>+7.02%</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1130000</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
@@ -2727,33 +2799,15 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>雙鴻</t>
-        </is>
-      </c>
+      <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>0.29%</t>
-        </is>
-      </c>
+      <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="n">
-        <v>18000</v>
-      </c>
+      <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
@@ -2765,72 +2819,72 @@
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>雙鴻科技</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>雙鴻</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>0.54%</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>0.63%</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>+0.09%</t>
-        </is>
-      </c>
-      <c r="BJ13" t="n">
-        <v>35000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>38000</v>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr"/>
-      <c r="BN13" t="inlineStr"/>
-      <c r="BO13" t="inlineStr"/>
-      <c r="BP13" t="inlineStr"/>
-      <c r="BQ13" t="inlineStr"/>
-      <c r="BR13" t="inlineStr"/>
-      <c r="BS13" t="inlineStr"/>
-      <c r="BT13" t="inlineStr"/>
-      <c r="BU13" t="inlineStr"/>
-      <c r="BV13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>7.99%</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>7.06%</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>-0.93%</t>
+        </is>
+      </c>
+      <c r="BT13" t="n">
+        <v>442000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>413000</v>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>-29,000</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2838,55 +2892,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>00981A,00993A</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3.36%</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>3.14%</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>-0.22%</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>13966000</v>
-      </c>
-      <c r="M14" t="n">
-        <v>12966000</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-1,000,000</t>
-        </is>
-      </c>
+          <t>00403A,00993A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -2907,16 +2925,52 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>6.81%</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>5.84%</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>-0.97%</t>
+        </is>
+      </c>
+      <c r="AP14" t="n">
+        <v>2850000</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-350,000</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
       <c r="AU14" t="inlineStr"/>
@@ -2939,38 +2993,38 @@
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>5.33%</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>5.65%</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="BJ14" t="n">
-        <v>76000</v>
+        <v>158000</v>
       </c>
       <c r="BK14" t="n">
-        <v>85000</v>
+        <v>164000</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr"/>
@@ -2987,12 +3041,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3020,43 +3074,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>旺矽科技</t>
+          <t>欣興電子</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>7.82%</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>+7.66%</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>250000</v>
+        <v>5100000</v>
       </c>
       <c r="W15" t="n">
-        <v>150000</v>
+        <v>5200000</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>-100,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -3101,38 +3155,38 @@
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>4.37%</t>
+          <t>5.54%</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>5.96%</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="BJ15" t="n">
-        <v>80000</v>
+        <v>492000</v>
       </c>
       <c r="BK15" t="n">
-        <v>82000</v>
+        <v>519000</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr"/>
@@ -3149,12 +3203,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3162,7 +3216,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>00400A,00993A</t>
+          <t>00991A,00993A</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -3175,16 +3229,52 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>+0.31%</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>5.55%</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>+5.24%</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
@@ -3227,96 +3317,60 @@
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>台塑石化</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>3.77%</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="BJ16" t="n">
-        <v>339000</v>
+        <v>428000</v>
       </c>
       <c r="BK16" t="n">
-        <v>378000</v>
+        <v>431000</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>39,000</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>1.46%</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>2.02%</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>+0.56%</t>
-        </is>
-      </c>
-      <c r="BT16" t="n">
-        <v>4903000</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>6147000</v>
-      </c>
-      <c r="BV16" t="inlineStr">
-        <is>
-          <t>1,244,000</t>
-        </is>
-      </c>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr"/>
+      <c r="BQ16" t="inlineStr"/>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3324,7 +3378,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>00403A,00985A</t>
+          <t>00991A,00993A</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -3337,108 +3391,72 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1.67%</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>1.85%</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>+0.18%</t>
-        </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>1625000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>75,000</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>高力熱處理工業</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>1.10%</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>0.79%</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>-0.31%</t>
-        </is>
-      </c>
-      <c r="AP17" t="n">
-        <v>76000</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>55000</v>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-21,000</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>+1.07%</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>250000</v>
+      </c>
+      <c r="W17" t="n">
+        <v>150000</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr"/>
       <c r="AU17" t="inlineStr"/>
@@ -3449,16 +3467,52 @@
       <c r="AZ17" t="inlineStr"/>
       <c r="BA17" t="inlineStr"/>
       <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
-      <c r="BI17" t="inlineStr"/>
-      <c r="BJ17" t="inlineStr"/>
-      <c r="BK17" t="inlineStr"/>
-      <c r="BL17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>4.37%</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>4.30%</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="BJ17" t="n">
+        <v>80000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>82000</v>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
       <c r="BM17" t="inlineStr"/>
       <c r="BN17" t="inlineStr"/>
       <c r="BO17" t="inlineStr"/>
@@ -3470,6 +3524,492 @@
       <c r="BU17" t="inlineStr"/>
       <c r="BV17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00981A,00982A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3.03%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>3.22%</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>5886000</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6151000</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>265,000</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
+        <v>421000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>418000</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>-3,000</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+      <c r="BO18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr"/>
+      <c r="BQ18" t="inlineStr"/>
+      <c r="BR18" t="inlineStr"/>
+      <c r="BS18" t="inlineStr"/>
+      <c r="BT18" t="inlineStr"/>
+      <c r="BU18" t="inlineStr"/>
+      <c r="BV18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6505</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>台塑化</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00400A,00993A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>台塑石化</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>台塑化</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="BJ19" t="n">
+        <v>339000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>378000</v>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>39,000</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>台塑化</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>台塑化</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>2.02%</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>+0.56%</t>
+        </is>
+      </c>
+      <c r="BT19" t="n">
+        <v>4903000</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>6147000</v>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>1,244,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00991A,00993A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>南亞電路</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>5.57%</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>+5.44%</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2.90%</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>3.05%</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
+      <c r="BJ20" t="n">
+        <v>247000</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>254000</v>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
+      <c r="BO20" t="inlineStr"/>
+      <c r="BP20" t="inlineStr"/>
+      <c r="BQ20" t="inlineStr"/>
+      <c r="BR20" t="inlineStr"/>
+      <c r="BS20" t="inlineStr"/>
+      <c r="BT20" t="inlineStr"/>
+      <c r="BU20" t="inlineStr"/>
+      <c r="BV20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
